--- a/artfynd/A 14858-2023 artfynd.xlsx
+++ b/artfynd/A 14858-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117019760</v>
+        <v>119431651</v>
       </c>
       <c r="B2" t="n">
-        <v>100061</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Årsta, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589496</v>
+        <v>589537</v>
       </c>
       <c r="R2" t="n">
-        <v>6542097</v>
+        <v>6542055</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117019759</v>
+        <v>117019750</v>
       </c>
       <c r="B3" t="n">
-        <v>100061</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589495</v>
+        <v>589544</v>
       </c>
       <c r="R3" t="n">
-        <v>6542081</v>
+        <v>6542115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +826,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Katrineholm</t>
+          <t>Flen</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -842,7 +836,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Sköldinge</t>
+          <t>Flen</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117019755</v>
+        <v>117019763</v>
       </c>
       <c r="B4" t="n">
-        <v>100061</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589507</v>
+        <v>589498</v>
       </c>
       <c r="R4" t="n">
-        <v>6542051</v>
+        <v>6542033</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117019764</v>
+        <v>117019754</v>
       </c>
       <c r="B5" t="n">
-        <v>100061</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589520</v>
+        <v>589479</v>
       </c>
       <c r="R5" t="n">
-        <v>6542024</v>
+        <v>6542064</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117019757</v>
+        <v>117019755</v>
       </c>
       <c r="B6" t="n">
-        <v>100061</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589513</v>
+        <v>589507</v>
       </c>
       <c r="R6" t="n">
-        <v>6542048</v>
+        <v>6542051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117019758</v>
+        <v>117019757</v>
       </c>
       <c r="B7" t="n">
-        <v>100061</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589514</v>
+        <v>589513</v>
       </c>
       <c r="R7" t="n">
-        <v>6542081</v>
+        <v>6542048</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,57 +1261,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119431651</v>
+        <v>117019758</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Årsta, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589537</v>
+        <v>589514</v>
       </c>
       <c r="R8" t="n">
-        <v>6542055</v>
+        <v>6542081</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1326,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,15 +1346,306 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Anna Sjövall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Anna Sjövall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>117019759</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589495</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6542081</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>117019760</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>589496</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6542097</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>117019764</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589520</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6542024</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14858-2023 artfynd.xlsx
+++ b/artfynd/A 14858-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119431651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019750</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019763</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019754</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019755</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019757</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019758</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019759</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019760</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,8 +1696,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117019764</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>